--- a/data/trans_camb/IP1008-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,0</t>
+          <t>-7,76; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,87</t>
+          <t>-0,53; 11,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,38</t>
+          <t>0,32; 6,49</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,0</t>
+          <t>-3,84; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,41</t>
+          <t>-0,68; 1,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,0</t>
+          <t>-1,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,43</t>
+          <t>0,92; 7,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,98</t>
+          <t>0,94; 5,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-3,28; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,18</t>
+          <t>-1,28; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,58</t>
+          <t>-1,56; 1,57</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 0,0</t>
+          <t>-7,84; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,0</t>
+          <t>-7,83; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,0</t>
+          <t>-5,62; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,0</t>
+          <t>-4,11; 0,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,58; 4,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-2,48; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,89</t>
+          <t>-1,58; 1,82</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,0</t>
+          <t>-3,74; -0,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,04</t>
+          <t>-2,49; 1,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,4</t>
+          <t>-2,31; -0,41</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,02</t>
+          <t>-1,45; 0,92</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-84,92; 429,38</t>
+          <t>-88,09; 284,33</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,67</t>
+          <t>-0,5; 0,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,22</t>
+          <t>-0,26; 1,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,41</t>
+          <t>-0,77; 0,41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,15</t>
+          <t>-0,87; 0,15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,34</t>
+          <t>-0,51; 0,35</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,5</t>
+          <t>-0,39; 0,48</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 372,18</t>
+          <t>-77,53; 524,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 698,16</t>
+          <t>-46,36; 667,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 188,45</t>
+          <t>-81,62; 184,4</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,21</t>
+          <t>-100,0; 94,32</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 108,17</t>
+          <t>-65,25; 123,68</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 167,65</t>
+          <t>-55,52; 164,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Provincia-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,0</t>
+          <t>-7,46; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 11,56</t>
+          <t>-0,24; 11,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 6,49</t>
+          <t>0,34; 6,32</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,21</t>
+          <t>-2,57; 1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,0</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,38</t>
+          <t>-0,66; 1,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,0</t>
+          <t>-1,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,68</t>
+          <t>0,91; 7,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,64</t>
+          <t>0,95; 5,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,0</t>
+          <t>-3,35; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,54</t>
+          <t>-0,72; 5,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,0</t>
+          <t>-5,1; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,57</t>
+          <t>-1,36; 1,94</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,0</t>
+          <t>-6,36; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,0</t>
+          <t>-7,71; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,0</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,0</t>
+          <t>-4,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,95</t>
+          <t>0,59; 5,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,0</t>
+          <t>-2,5; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,0</t>
+          <t>-1,14; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,0</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,82</t>
+          <t>-1,63; 1,9</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,41</t>
+          <t>-3,34; -0,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,12</t>
+          <t>-2,5; 1,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,41</t>
+          <t>-2,64; -0,41</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,92</t>
+          <t>-1,46; 0,95</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-88,09; 284,33</t>
+          <t>-87,19; 303,54</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,68</t>
+          <t>-0,55; 0,69</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,15</t>
+          <t>-0,22; 1,24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,41</t>
+          <t>-0,76; 0,42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,15</t>
+          <t>-0,96; 0,19</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,35</t>
+          <t>-0,45; 0,32</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,48</t>
+          <t>-0,38; 0,49</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 524,61</t>
+          <t>-76,44; 451,27</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 667,12</t>
+          <t>-39,9; 705,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-81,62; 184,4</t>
+          <t>-80,98; 224,47</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,32</t>
+          <t>-100,0; 156,29</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 123,68</t>
+          <t>-63,35; 109,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 164,95</t>
+          <t>-55,78; 188,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>4,86</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,47</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,02; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>-0,24; 11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,32</t>
+          <t>0,34; 6,38</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>346,45%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,21</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>-2,03; 1,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,29; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,39</t>
+          <t>-0,66; 1,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,0</t>
+          <t>-1,76; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-7,98%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,79</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,12</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,92; 8,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,59</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,49</t>
+          <t>0,96; 5,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,9</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,0</t>
+          <t>-4,33; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,31</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,0</t>
+          <t>-3,59; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>-1,28; 4,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,94</t>
+          <t>-1,37; 1,58</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>127,91%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,9; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,85; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-4,37; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,0</t>
+          <t>-4,06; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>2,55</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,01</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-1,28; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,28; 0,0</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,25</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-3,32; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,9</t>
+          <t>-2,51; 1,04</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,41</t>
+          <t>-3,48; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,18</t>
+          <t>-1,54; 1,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,41</t>
+          <t>-2,31; -0,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,95</t>
+          <t>-1,4; 1,02</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>-38,48%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>4,6%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-38,48%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-87,19; 303,54</t>
+          <t>-84,92; 429,38</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,69</t>
+          <t>-0,78; 0,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,24</t>
+          <t>-0,95; 0,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,42</t>
+          <t>-0,57; 0,67</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,19</t>
+          <t>-0,27; 1,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,32</t>
+          <t>-0,49; 0,34</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,49</t>
+          <t>-0,39; 0,5</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-23,05%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-53,89%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>87,18%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-23,05%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-53,89%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 451,27</t>
+          <t>-80,72; 188,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 705,62</t>
+          <t>-100,0; 121,21</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 224,47</t>
+          <t>-77,98; 372,18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,29</t>
+          <t>-46,07; 698,16</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 109,5</t>
+          <t>-62,78; 108,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 188,55</t>
+          <t>-56,52; 167,65</t>
         </is>
       </c>
     </row>
